--- a/inputs/vehicles.xlsx
+++ b/inputs/vehicles.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$2</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>vehicle_id</t>
   </si>
@@ -33,34 +33,10 @@
     <t>V1</t>
   </si>
   <si>
-    <t>V2</t>
-  </si>
-  <si>
-    <t>V3</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
-    <t>electric</t>
-  </si>
-  <si>
     <t>ring</t>
-  </si>
-  <si>
-    <t>V4</t>
-  </si>
-  <si>
-    <t>V5</t>
-  </si>
-  <si>
-    <t>V6</t>
-  </si>
-  <si>
-    <t>V7</t>
-  </si>
-  <si>
-    <t>V8</t>
   </si>
 </sst>
 </file>
@@ -428,17 +404,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -449,96 +425,19 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
       <c r="C2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
         <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C9">
-    <sortState ref="A2:C9">
-      <sortCondition ref="B1:B9"/>
+  <autoFilter ref="A1:C2">
+    <sortState ref="A2:C5">
+      <sortCondition ref="B1:B2"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inputs/vehicles.xlsx
+++ b/inputs/vehicles.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\logistics-model2\internal-logistics-model2\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Er\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -39,13 +39,13 @@
     <t>ring</t>
   </si>
   <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
     <t>electric</t>
-  </si>
-  <si>
-    <t>V2</t>
-  </si>
-  <si>
-    <t>V3</t>
   </si>
 </sst>
 </file>
@@ -448,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>15</v>
